--- a/outputs/Data Specs_完成版_2026-06-11.xlsx
+++ b/outputs/Data Specs_完成版_2026-06-11.xlsx
@@ -37447,7 +37447,7 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>In Japan, which day is more important, Christmas or New Year's Day? A: New Year's Day is more important than Christmas in Japan.</t>
+          <t>In Japan, which day is more important, Christmas or New Year's Day?</t>
         </is>
       </c>
       <c r="F1427" t="inlineStr">
@@ -73285,7 +73285,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>New Year is more important than Christmas in Japan.</t>
+          <t>New Year's Day is more important than Christmas in Japan.</t>
         </is>
       </c>
     </row>

--- a/outputs/Data Specs_完成版_2026-06-11.xlsx
+++ b/outputs/Data Specs_完成版_2026-06-11.xlsx
@@ -17443,7 +17443,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Do you like sports? What sports do you like?</t>
+          <t>Do you like sports?</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>What do you know about them? I know that they are popular.</t>
+          <t>What do you know about them?</t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>Which animal is the biggest in Ueno Zoo? The elephant is the biggest animal in Ueno Zoo.</t>
+          <t>Which animal is the biggest in Ueno Zoo?</t>
         </is>
       </c>
       <c r="F1422" t="inlineStr">
@@ -37375,7 +37375,7 @@
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>Which country is the biggest in Europe? Russia is the biggest country in Europe.</t>
+          <t>Which country is the biggest in Europe?</t>
         </is>
       </c>
       <c r="F1424" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>Who is the most famous singer in Japan? Kenshi Yonezu is the most famous singer in Japan.</t>
+          <t>Who is the most famous singer in Japan?</t>
         </is>
       </c>
       <c r="F1469" t="inlineStr">
@@ -47183,7 +47183,7 @@
       </c>
       <c r="E1874" t="inlineStr">
         <is>
-          <t>What is fun to do? It's fun to swim in the pool.</t>
+          <t>What is fun to do?</t>
         </is>
       </c>
       <c r="F1874" t="inlineStr">
@@ -47207,7 +47207,7 @@
       </c>
       <c r="E1875" t="inlineStr">
         <is>
-          <t>What is important to do? It's important to eat breakfast every day.</t>
+          <t>What is important to do?</t>
         </is>
       </c>
       <c r="F1875" t="inlineStr">
@@ -47231,7 +47231,7 @@
       </c>
       <c r="E1876" t="inlineStr">
         <is>
-          <t>What is exciting to do? It's exciting to visit a new country.</t>
+          <t>What is exciting to do?</t>
         </is>
       </c>
       <c r="F1876" t="inlineStr">
@@ -47255,7 +47255,7 @@
       </c>
       <c r="E1877" t="inlineStr">
         <is>
-          <t>What is hard to do? It's hard to wake up early in winter.</t>
+          <t>What is hard to do?</t>
         </is>
       </c>
       <c r="F1877" t="inlineStr">
@@ -47279,7 +47279,7 @@
       </c>
       <c r="E1878" t="inlineStr">
         <is>
-          <t>What is helpful to do? It's helpful to clean my room every day.</t>
+          <t>What is helpful to do?</t>
         </is>
       </c>
       <c r="F1878" t="inlineStr">
@@ -47303,7 +47303,7 @@
       </c>
       <c r="E1879" t="inlineStr">
         <is>
-          <t>What is dangerous to do? It's dangerous to run on the road.</t>
+          <t>What is dangerous to do?</t>
         </is>
       </c>
       <c r="F1879" t="inlineStr">
@@ -47327,7 +47327,7 @@
       </c>
       <c r="E1880" t="inlineStr">
         <is>
-          <t>What is nice to do? It's nice to listen to music after school.</t>
+          <t>What is nice to do?</t>
         </is>
       </c>
       <c r="F1880" t="inlineStr">
@@ -47351,7 +47351,7 @@
       </c>
       <c r="E1881" t="inlineStr">
         <is>
-          <t>What is useful to do? It's useful to learn another language.</t>
+          <t>What is useful to do?</t>
         </is>
       </c>
       <c r="F1881" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="E1882" t="inlineStr">
         <is>
-          <t>What is easy for you to do? It's easy for me to cook pasta.</t>
+          <t>What is easy for you to do?</t>
         </is>
       </c>
       <c r="F1882" t="inlineStr">
@@ -47399,7 +47399,7 @@
       </c>
       <c r="E1883" t="inlineStr">
         <is>
-          <t>What is difficult for him to do? It's difficult for him to finish the homework.</t>
+          <t>What is difficult for him to do?</t>
         </is>
       </c>
       <c r="F1883" t="inlineStr">
@@ -47423,7 +47423,7 @@
       </c>
       <c r="E1884" t="inlineStr">
         <is>
-          <t>What is important for us to do? It's important for us to practice every day.</t>
+          <t>What is important for us to do?</t>
         </is>
       </c>
       <c r="F1884" t="inlineStr">
@@ -47447,7 +47447,7 @@
       </c>
       <c r="E1885" t="inlineStr">
         <is>
-          <t>What is exciting for them to do? It's exciting for them to join the soccer team.</t>
+          <t>What is exciting for them to do?</t>
         </is>
       </c>
       <c r="F1885" t="inlineStr">
@@ -47471,7 +47471,7 @@
       </c>
       <c r="E1886" t="inlineStr">
         <is>
-          <t>What is dangerous for you to do? It's dangerous for me to ride a skateboard.</t>
+          <t>What is dangerous for you to do?</t>
         </is>
       </c>
       <c r="F1886" t="inlineStr">
@@ -47495,7 +47495,7 @@
       </c>
       <c r="E1887" t="inlineStr">
         <is>
-          <t>What is fun for your sister to do? It's fun for my sister to play the piano.</t>
+          <t>What is fun for your sister to do?</t>
         </is>
       </c>
       <c r="F1887" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="E1888" t="inlineStr">
         <is>
-          <t>What is hard for you to do? It's hard for me to wake up early on Sundays.</t>
+          <t>What is hard for you to do?</t>
         </is>
       </c>
       <c r="F1888" t="inlineStr">
@@ -47543,7 +47543,7 @@
       </c>
       <c r="E1889" t="inlineStr">
         <is>
-          <t>What is helpful for your brother to do? It's helpful for my brother to study with friends.</t>
+          <t>What is helpful for your brother to do?</t>
         </is>
       </c>
       <c r="F1889" t="inlineStr">
@@ -48027,7 +48027,7 @@
       </c>
       <c r="E1913" t="inlineStr">
         <is>
-          <t>Do you want that jacket? Would you like that jacket?</t>
+          <t>Do you want that jacket?</t>
         </is>
       </c>
       <c r="F1913" t="inlineStr"/>
@@ -48607,7 +48607,7 @@
       </c>
       <c r="E1940" t="inlineStr">
         <is>
-          <t>What did Mary tell Tom? She told him to come early tomorrow.</t>
+          <t>What did Mary tell Tom?</t>
         </is>
       </c>
       <c r="F1940" t="inlineStr">
@@ -49719,7 +49719,7 @@
       </c>
       <c r="E1989" t="inlineStr">
         <is>
-          <t>What did she tell you? She told me that she had lost her wallet.</t>
+          <t>What did she tell you?</t>
         </is>
       </c>
       <c r="F1989" t="inlineStr">
@@ -61221,7 +61221,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>What subjects do you like?</t>
+          <t>What sports do you like?</t>
         </is>
       </c>
     </row>
@@ -69710,7 +69710,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>I know that he is popular.</t>
+          <t>I know that they are popular.</t>
         </is>
       </c>
     </row>
@@ -73220,7 +73220,7 @@
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>The elephant is the biggest animal in the zoo.</t>
+          <t>The elephant is the biggest animal in Ueno Zoo.</t>
         </is>
       </c>
     </row>
@@ -73246,7 +73246,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Russia is the biggest country in the world.</t>
+          <t>Russia is the biggest country in Europe.</t>
         </is>
       </c>
     </row>
@@ -79252,7 +79252,7 @@
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>It's dangerous for me to skateboard.</t>
+          <t>It's dangerous for me to ride a skateboard.</t>
         </is>
       </c>
     </row>
@@ -79954,7 +79954,7 @@
       </c>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>He told him to come early tomorrow.</t>
+          <t>She told him to come early tomorrow.</t>
         </is>
       </c>
     </row>
@@ -80591,7 +80591,7 @@
       </c>
       <c r="C1989" t="inlineStr">
         <is>
-          <t>She told me that she lost her wallet.</t>
+          <t>She told me that she had lost her wallet.</t>
         </is>
       </c>
     </row>
